--- a/public/StructureDefinition-pghd-observation-state-of-mind.xlsx
+++ b/public/StructureDefinition-pghd-observation-state-of-mind.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-observation-state-of-mind.xlsx
+++ b/public/StructureDefinition-pghd-observation-state-of-mind.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8736" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8736" uniqueCount="743">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6782,7 +6785,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6816,7 +6819,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6893,10 +6896,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7013,10 +7016,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7056,7 +7059,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -7133,10 +7136,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7253,10 +7256,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7375,13 +7378,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7499,7 +7502,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>307</v>
@@ -7617,7 +7620,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>309</v>
@@ -7737,7 +7740,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>311</v>
@@ -7782,7 +7785,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7859,10 +7862,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7979,10 +7982,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8099,10 +8102,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8219,10 +8222,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8341,10 +8344,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8463,10 +8466,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8489,19 +8492,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8550,7 +8553,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8565,19 +8568,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8585,10 +8588,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8611,16 +8614,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8670,7 +8673,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8694,10 +8697,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8705,14 +8708,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8731,19 +8734,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8792,7 +8795,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8807,19 +8810,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8827,14 +8830,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8853,19 +8856,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8914,7 +8917,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8929,19 +8932,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8949,10 +8952,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8975,16 +8978,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9034,7 +9037,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9055,13 +9058,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9069,10 +9072,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9095,17 +9098,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9154,7 +9157,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9169,19 +9172,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9189,10 +9192,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9215,19 +9218,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9276,7 +9279,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9285,7 +9288,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9294,27 +9297,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9340,16 +9343,16 @@
         <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9374,13 +9377,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9398,7 +9401,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9407,7 +9410,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9422,7 +9425,7 @@
         <v>135</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9433,14 +9436,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9462,16 +9465,16 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9496,13 +9499,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9520,7 +9523,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9538,27 +9541,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9581,19 +9584,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9642,7 +9645,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9663,10 +9666,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9677,10 +9680,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9706,13 +9709,13 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9741,10 +9744,10 @@
         <v>290</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9762,7 +9765,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9780,27 +9783,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9826,16 +9829,16 @@
         <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9863,10 +9866,10 @@
         <v>290</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9884,7 +9887,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9905,10 +9908,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9919,10 +9922,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9945,16 +9948,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10004,7 +10007,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10022,27 +10025,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10065,16 +10068,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10124,7 +10127,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10142,27 +10145,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10185,19 +10188,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10246,7 +10249,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10258,7 +10261,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10267,10 +10270,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10281,10 +10284,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10399,10 +10402,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10519,14 +10522,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10548,10 +10551,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>141</v>
@@ -10606,7 +10609,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10641,10 +10644,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10667,13 +10670,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10724,7 +10727,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10733,7 +10736,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10745,10 +10748,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10759,10 +10762,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10785,13 +10788,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10842,7 +10845,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10851,7 +10854,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10863,10 +10866,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10877,10 +10880,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10906,16 +10909,16 @@
         <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10943,10 +10946,10 @@
         <v>116</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10964,7 +10967,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10982,13 +10985,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10999,10 +11002,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11028,16 +11031,16 @@
         <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11065,10 +11068,10 @@
         <v>290</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -11086,7 +11089,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11104,13 +11107,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11121,10 +11124,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11147,17 +11150,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11206,7 +11209,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11230,7 +11233,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11241,10 +11244,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11270,10 +11273,10 @@
         <v>205</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11324,7 +11327,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11345,10 +11348,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11359,10 +11362,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11385,16 +11388,16 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11444,7 +11447,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11465,10 +11468,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11479,10 +11482,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11505,16 +11508,16 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11564,7 +11567,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11585,10 +11588,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11599,10 +11602,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11610,7 +11613,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>81</v>
@@ -11625,19 +11628,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11674,7 +11677,7 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11684,7 +11687,7 @@
         <v>198</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11705,10 +11708,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11719,10 +11722,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11837,10 +11840,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11957,14 +11960,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11986,10 +11989,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
@@ -12044,7 +12047,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12079,10 +12082,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12108,13 +12111,13 @@
         <v>190</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>289</v>
@@ -12166,7 +12169,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>92</v>
@@ -12184,7 +12187,7 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>295</v>
@@ -12201,10 +12204,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12227,19 +12230,19 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12288,7 +12291,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12306,27 +12309,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12352,16 +12355,16 @@
         <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12386,13 +12389,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12410,7 +12413,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12419,7 +12422,7 @@
         <v>92</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>104</v>
@@ -12434,7 +12437,7 @@
         <v>135</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12445,14 +12448,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12474,16 +12477,16 @@
         <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12508,13 +12511,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12532,7 +12535,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12550,27 +12553,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12596,16 +12599,16 @@
         <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12654,7 +12657,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12675,10 +12678,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12689,13 +12692,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
@@ -12717,19 +12720,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12778,7 +12781,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12799,10 +12802,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12813,10 +12816,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12931,10 +12934,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13051,14 +13054,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13080,10 +13083,10 @@
         <v>138</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>141</v>
@@ -13138,7 +13141,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13173,10 +13176,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13202,13 +13205,13 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>289</v>
@@ -13240,7 +13243,7 @@
       </c>
       <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -13258,7 +13261,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>92</v>
@@ -13276,7 +13279,7 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>295</v>
@@ -13293,10 +13296,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13411,10 +13414,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13531,10 +13534,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13653,10 +13656,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13771,10 +13774,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13891,10 +13894,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13936,7 +13939,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>82</v>
@@ -14013,10 +14016,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14133,10 +14136,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14176,7 +14179,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>82</v>
@@ -14253,10 +14256,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14373,10 +14376,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14495,10 +14498,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14617,10 +14620,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14646,16 +14649,16 @@
         <v>190</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14684,7 +14687,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14702,7 +14705,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14720,27 +14723,27 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14855,10 +14858,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14975,10 +14978,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15097,10 +15100,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15215,10 +15218,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15335,10 +15338,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15383,7 +15386,7 @@
         <v>82</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>82</v>
@@ -15457,10 +15460,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15577,10 +15580,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15697,10 +15700,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15817,10 +15820,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15939,10 +15942,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16061,10 +16064,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16090,16 +16093,16 @@
         <v>190</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16124,13 +16127,13 @@
         <v>82</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16148,7 +16151,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16157,7 +16160,7 @@
         <v>92</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>104</v>
@@ -16172,7 +16175,7 @@
         <v>135</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16183,14 +16186,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16212,16 +16215,16 @@
         <v>190</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16246,13 +16249,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16270,7 +16273,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16288,27 +16291,27 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16334,16 +16337,16 @@
         <v>83</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16392,7 +16395,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16413,10 +16416,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16427,13 +16430,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>82</v>
@@ -16455,19 +16458,19 @@
         <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16516,7 +16519,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16537,10 +16540,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16551,10 +16554,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16669,10 +16672,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16789,14 +16792,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16818,10 +16821,10 @@
         <v>138</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>141</v>
@@ -16876,7 +16879,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16911,10 +16914,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16940,13 +16943,13 @@
         <v>190</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O119" t="s" s="2">
         <v>289</v>
@@ -16978,7 +16981,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16996,7 +16999,7 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>92</v>
@@ -17014,7 +17017,7 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>295</v>
@@ -17031,10 +17034,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17149,10 +17152,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17269,10 +17272,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17391,10 +17394,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17509,10 +17512,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17629,10 +17632,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17674,7 +17677,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>82</v>
@@ -17751,10 +17754,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17871,10 +17874,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17914,7 +17917,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>82</v>
@@ -17991,10 +17994,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18111,10 +18114,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18233,10 +18236,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18355,10 +18358,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18381,19 +18384,19 @@
         <v>93</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
@@ -18442,7 +18445,7 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18460,27 +18463,27 @@
         <v>82</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18506,16 +18509,16 @@
         <v>190</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
@@ -18540,13 +18543,13 @@
         <v>82</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>82</v>
@@ -18564,7 +18567,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18573,7 +18576,7 @@
         <v>92</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>104</v>
@@ -18588,7 +18591,7 @@
         <v>135</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18599,14 +18602,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18628,16 +18631,16 @@
         <v>190</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18662,13 +18665,13 @@
         <v>82</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>82</v>
@@ -18686,7 +18689,7 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18704,27 +18707,27 @@
         <v>82</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18750,16 +18753,16 @@
         <v>83</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18808,7 +18811,7 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18829,10 +18832,10 @@
         <v>82</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18843,13 +18846,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>82</v>
@@ -18871,19 +18874,19 @@
         <v>93</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18932,7 +18935,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18953,10 +18956,10 @@
         <v>82</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18967,10 +18970,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19085,10 +19088,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19205,14 +19208,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -19234,10 +19237,10 @@
         <v>138</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>141</v>
@@ -19292,7 +19295,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19327,10 +19330,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19356,13 +19359,13 @@
         <v>190</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O139" t="s" s="2">
         <v>289</v>
@@ -19394,7 +19397,7 @@
       </c>
       <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19412,7 +19415,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>92</v>
@@ -19430,7 +19433,7 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>295</v>
@@ -19447,10 +19450,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19565,10 +19568,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19685,10 +19688,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19807,10 +19810,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19925,10 +19928,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20045,10 +20048,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20090,7 +20093,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>82</v>
@@ -20167,10 +20170,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20287,10 +20290,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20330,7 +20333,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>82</v>
@@ -20407,10 +20410,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20527,10 +20530,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20649,10 +20652,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20771,10 +20774,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20800,16 +20803,16 @@
         <v>190</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>82</v>
@@ -20838,7 +20841,7 @@
       </c>
       <c r="Y151" s="2"/>
       <c r="Z151" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>82</v>
@@ -20856,7 +20859,7 @@
         <v>82</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20874,27 +20877,27 @@
         <v>82</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21009,10 +21012,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21129,10 +21132,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21251,10 +21254,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21369,10 +21372,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21489,10 +21492,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21534,7 +21537,7 @@
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>82</v>
@@ -21611,10 +21614,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21731,10 +21734,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21851,10 +21854,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21971,10 +21974,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22093,10 +22096,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22215,10 +22218,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22244,16 +22247,16 @@
         <v>190</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>82</v>
@@ -22278,13 +22281,13 @@
         <v>82</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>82</v>
@@ -22302,7 +22305,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22311,7 +22314,7 @@
         <v>92</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>104</v>
@@ -22326,7 +22329,7 @@
         <v>135</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22337,14 +22340,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -22366,16 +22369,16 @@
         <v>190</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
@@ -22400,13 +22403,13 @@
         <v>82</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>82</v>
@@ -22424,7 +22427,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22442,27 +22445,27 @@
         <v>82</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22488,16 +22491,16 @@
         <v>83</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
@@ -22546,7 +22549,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22567,10 +22570,10 @@
         <v>82</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22581,13 +22584,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>82</v>
@@ -22609,19 +22612,19 @@
         <v>93</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22670,7 +22673,7 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22691,10 +22694,10 @@
         <v>82</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
@@ -22705,10 +22708,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22823,10 +22826,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22943,14 +22946,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -22972,10 +22975,10 @@
         <v>138</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>141</v>
@@ -23030,7 +23033,7 @@
         <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23065,10 +23068,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23094,13 +23097,13 @@
         <v>190</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O170" t="s" s="2">
         <v>289</v>
@@ -23132,7 +23135,7 @@
       </c>
       <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>82</v>
@@ -23150,7 +23153,7 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>92</v>
@@ -23168,7 +23171,7 @@
         <v>82</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>295</v>
@@ -23185,10 +23188,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23303,10 +23306,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23423,10 +23426,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23545,10 +23548,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23663,10 +23666,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23783,10 +23786,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23828,7 +23831,7 @@
       </c>
       <c r="Q176" s="2"/>
       <c r="R176" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S176" t="s" s="2">
         <v>82</v>
@@ -23905,10 +23908,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24025,10 +24028,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24068,7 +24071,7 @@
       </c>
       <c r="Q178" s="2"/>
       <c r="R178" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="S178" t="s" s="2">
         <v>82</v>
@@ -24145,10 +24148,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24265,10 +24268,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24387,10 +24390,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24509,10 +24512,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24538,16 +24541,16 @@
         <v>190</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24576,7 +24579,7 @@
       </c>
       <c r="Y182" s="2"/>
       <c r="Z182" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>82</v>
@@ -24594,7 +24597,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24612,27 +24615,27 @@
         <v>82</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24747,10 +24750,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24867,10 +24870,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24989,10 +24992,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25107,10 +25110,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25227,10 +25230,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25275,7 +25278,7 @@
         <v>82</v>
       </c>
       <c r="S188" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="T188" t="s" s="2">
         <v>82</v>
@@ -25349,10 +25352,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25469,10 +25472,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25589,10 +25592,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25709,10 +25712,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25831,10 +25834,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25953,10 +25956,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25982,16 +25985,16 @@
         <v>190</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -26016,13 +26019,13 @@
         <v>82</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -26040,7 +26043,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26049,7 +26052,7 @@
         <v>92</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>104</v>
@@ -26064,7 +26067,7 @@
         <v>135</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>82</v>
@@ -26075,14 +26078,14 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -26104,16 +26107,16 @@
         <v>190</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>82</v>
@@ -26138,13 +26141,13 @@
         <v>82</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>82</v>
@@ -26162,7 +26165,7 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26180,27 +26183,27 @@
         <v>82</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP195" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26226,16 +26229,16 @@
         <v>83</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>82</v>
@@ -26284,7 +26287,7 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26305,10 +26308,10 @@
         <v>82</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
@@ -26319,13 +26322,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>82</v>
@@ -26347,19 +26350,19 @@
         <v>93</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>82</v>
@@ -26408,7 +26411,7 @@
         <v>82</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26429,10 +26432,10 @@
         <v>82</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>
@@ -26443,10 +26446,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26561,10 +26564,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26681,14 +26684,14 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
@@ -26710,10 +26713,10 @@
         <v>138</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N200" t="s" s="2">
         <v>141</v>
@@ -26768,7 +26771,7 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -26803,10 +26806,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26832,13 +26835,13 @@
         <v>190</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O201" t="s" s="2">
         <v>289</v>
@@ -26870,7 +26873,7 @@
       </c>
       <c r="Y201" s="2"/>
       <c r="Z201" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>82</v>
@@ -26888,7 +26891,7 @@
         <v>82</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>92</v>
@@ -26906,7 +26909,7 @@
         <v>82</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>295</v>
@@ -26923,10 +26926,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27041,10 +27044,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27161,10 +27164,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27283,10 +27286,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27401,10 +27404,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27521,10 +27524,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27566,7 +27569,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>82</v>
@@ -27643,10 +27646,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27763,10 +27766,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27806,7 +27809,7 @@
       </c>
       <c r="Q209" s="2"/>
       <c r="R209" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="S209" t="s" s="2">
         <v>82</v>
@@ -27883,10 +27886,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28003,10 +28006,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28125,10 +28128,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28247,10 +28250,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28276,16 +28279,16 @@
         <v>190</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>82</v>
@@ -28314,7 +28317,7 @@
       </c>
       <c r="Y213" s="2"/>
       <c r="Z213" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>82</v>
@@ -28332,7 +28335,7 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28350,27 +28353,27 @@
         <v>82</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP213" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28485,10 +28488,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28605,10 +28608,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28727,10 +28730,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28845,10 +28848,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28965,10 +28968,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29010,7 +29013,7 @@
       </c>
       <c r="Q219" s="2"/>
       <c r="R219" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="S219" t="s" s="2">
         <v>82</v>
@@ -29087,10 +29090,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29207,10 +29210,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29327,10 +29330,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29447,10 +29450,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29569,10 +29572,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29691,10 +29694,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29720,16 +29723,16 @@
         <v>190</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>82</v>
@@ -29754,13 +29757,13 @@
         <v>82</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>82</v>
@@ -29778,7 +29781,7 @@
         <v>82</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -29787,7 +29790,7 @@
         <v>92</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>104</v>
@@ -29802,7 +29805,7 @@
         <v>135</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>82</v>
@@ -29813,14 +29816,14 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
@@ -29842,16 +29845,16 @@
         <v>190</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>82</v>
@@ -29876,13 +29879,13 @@
         <v>82</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>82</v>
@@ -29900,7 +29903,7 @@
         <v>82</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -29918,27 +29921,27 @@
         <v>82</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP226" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29964,16 +29967,16 @@
         <v>83</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>82</v>
@@ -30022,7 +30025,7 @@
         <v>82</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -30043,10 +30046,10 @@
         <v>82</v>
       </c>
       <c r="AM227" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>82</v>
